--- a/positionlimit-previous.xlsx
+++ b/positionlimit-previous.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E739AD27-E7A6-40CF-8526-DDFB8C389FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AC4897-5DDB-4E20-8C4C-758471988402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="929" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="929" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Explanatory text" sheetId="1" r:id="rId1"/>
@@ -382,7 +382,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1124,14 +1124,14 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A3:AH23"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="13" max="13" width="4" customWidth="1"/>
     <col min="14" max="14" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="K3" s="32" t="s">
         <v>0</v>
       </c>
@@ -1139,7 +1139,7 @@
       <c r="M3" s="33"/>
       <c r="N3" s="33"/>
     </row>
-    <row r="9" spans="1:34" s="6" customFormat="1" ht="34.5" customHeight="1">
+    <row r="9" spans="1:34" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3" t="s">
         <v>1</v>
@@ -1177,12 +1177,12 @@
       <c r="AG9" s="2"/>
       <c r="AH9" s="2"/>
     </row>
-    <row r="11" spans="1:34" s="8" customFormat="1" ht="17.45">
+    <row r="11" spans="1:34" s="8" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:34" s="7" customFormat="1" ht="127.9" customHeight="1">
+    <row r="12" spans="1:34" s="7" customFormat="1" ht="127.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="37" t="s">
         <v>3</v>
       </c>
@@ -1199,7 +1199,7 @@
       <c r="M12" s="37"/>
       <c r="N12" s="37"/>
     </row>
-    <row r="13" spans="1:34" s="7" customFormat="1" ht="8.25" customHeight="1">
+    <row r="13" spans="1:34" s="7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="37"/>
       <c r="C13" s="37"/>
       <c r="D13" s="37"/>
@@ -1214,7 +1214,7 @@
       <c r="M13" s="37"/>
       <c r="N13" s="37"/>
     </row>
-    <row r="14" spans="1:34" s="7" customFormat="1" ht="17.45">
+    <row r="14" spans="1:34" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
@@ -1231,7 +1231,7 @@
       <c r="M14" s="34"/>
       <c r="N14" s="34"/>
     </row>
-    <row r="15" spans="1:34" s="7" customFormat="1" ht="75" customHeight="1">
+    <row r="15" spans="1:34" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="37" t="s">
         <v>5</v>
       </c>
@@ -1248,7 +1248,7 @@
       <c r="M15" s="37"/>
       <c r="N15" s="37"/>
     </row>
-    <row r="16" spans="1:34" s="7" customFormat="1" ht="10.5" customHeight="1">
+    <row r="16" spans="1:34" s="7" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="34"/>
       <c r="C16" s="34"/>
       <c r="D16" s="34"/>
@@ -1263,7 +1263,7 @@
       <c r="M16" s="34"/>
       <c r="N16" s="34"/>
     </row>
-    <row r="17" spans="2:14" s="7" customFormat="1" ht="22.5" customHeight="1">
+    <row r="17" spans="2:14" s="7" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>6</v>
       </c>
@@ -1280,7 +1280,7 @@
       <c r="M17" s="34"/>
       <c r="N17" s="34"/>
     </row>
-    <row r="18" spans="2:14" s="7" customFormat="1" ht="47.65" customHeight="1">
+    <row r="18" spans="2:14" s="7" customFormat="1" ht="47.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="37" t="s">
         <v>7</v>
       </c>
@@ -1297,7 +1297,7 @@
       <c r="M18" s="37"/>
       <c r="N18" s="37"/>
     </row>
-    <row r="19" spans="2:14" ht="8.65" customHeight="1">
+    <row r="19" spans="2:14" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="38"/>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -1311,7 +1311,7 @@
       <c r="L19" s="38"/>
       <c r="M19" s="38"/>
     </row>
-    <row r="20" spans="2:14" ht="17.45">
+    <row r="20" spans="2:14" ht="18" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>8</v>
       </c>
@@ -1325,7 +1325,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="2:14" ht="49.15" customHeight="1">
+    <row r="21" spans="2:14" ht="49.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="37" t="s">
         <v>9</v>
       </c>
@@ -1342,7 +1342,7 @@
       <c r="M21" s="37"/>
       <c r="N21" s="37"/>
     </row>
-    <row r="22" spans="2:14" ht="36" customHeight="1">
+    <row r="22" spans="2:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="37" t="s">
         <v>10</v>
       </c>
@@ -1359,7 +1359,7 @@
       <c r="M22" s="37"/>
       <c r="N22" s="37"/>
     </row>
-    <row r="23" spans="2:14" ht="50.25" customHeight="1">
+    <row r="23" spans="2:14" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="37" t="s">
         <v>11</v>
       </c>
@@ -1399,7 +1399,7 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
@@ -1408,7 +1408,7 @@
     <col min="6" max="6" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="39" t="s">
         <v>12</v>
       </c>
@@ -1418,7 +1418,7 @@
       <c r="E1" s="40"/>
       <c r="F1" s="40"/>
     </row>
-    <row r="2" spans="1:6" ht="19.899999999999999" customHeight="1">
+    <row r="2" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>13</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
+    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>19</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
         <v>25</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>29</v>
       </c>
@@ -1512,7 +1512,7 @@
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -1531,7 +1531,7 @@
     <col min="19" max="19" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18">
+    <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
         <v>31</v>
       </c>
@@ -1554,7 +1554,7 @@
       <c r="R1" s="46"/>
       <c r="S1" s="46"/>
     </row>
-    <row r="2" spans="1:19" s="13" customFormat="1" ht="13.9">
+    <row r="2" spans="1:19" s="13" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="42" t="s">
         <v>12</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="R2" s="35"/>
       <c r="S2" s="35"/>
     </row>
-    <row r="3" spans="1:19" s="13" customFormat="1" ht="69">
+    <row r="3" spans="1:19" s="13" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>13</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="13" customFormat="1" ht="25.9" customHeight="1">
+    <row r="4" spans="1:19" s="13" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
         <v>46</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="13" customFormat="1" ht="25.9" customHeight="1">
+    <row r="5" spans="1:19" s="13" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>29</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="13" customFormat="1" ht="27.6">
+    <row r="6" spans="1:19" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>57</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>52</v>
       </c>
       <c r="N6" s="14">
-        <v>120000</v>
+        <v>110000</v>
       </c>
       <c r="O6" s="21">
         <v>21</v>
@@ -1817,7 +1817,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="13" customFormat="1" ht="27.6">
+    <row r="7" spans="1:19" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>66</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="13" customFormat="1" ht="27.6">
+    <row r="8" spans="1:19" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>70</v>
       </c>
@@ -1935,9 +1935,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.9" customHeight="1"/>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1"/>
-    <row r="11" spans="1:19" ht="18">
+    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="46" t="s">
         <v>73</v>
       </c>
@@ -1960,7 +1960,7 @@
       <c r="R11" s="46"/>
       <c r="S11" s="46"/>
     </row>
-    <row r="12" spans="1:19" s="13" customFormat="1" ht="13.9">
+    <row r="12" spans="1:19" s="13" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="42" t="s">
         <v>12</v>
       </c>
@@ -1987,7 +1987,7 @@
       <c r="R12" s="35"/>
       <c r="S12" s="35"/>
     </row>
-    <row r="13" spans="1:19" s="13" customFormat="1" ht="69">
+    <row r="13" spans="1:19" s="13" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>13</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="13" customFormat="1" ht="27.6">
+    <row r="14" spans="1:19" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
         <v>75</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="27.4" customHeight="1">
+    <row r="16" spans="1:19" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
         <v>83</v>
       </c>
@@ -2128,7 +2128,7 @@
       <c r="R16" s="41"/>
       <c r="S16" s="41"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>84</v>
       </c>
@@ -2151,7 +2151,7 @@
       <c r="R17" s="22"/>
       <c r="S17" s="22"/>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>85</v>
       </c>
@@ -2201,73 +2201,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <caa5aeb1a6644849b60fbe2335e12657 xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">729cc5dc-fc40-4e6f-89b7-0bed773f437e</TermId>
-        </TermInfo>
-      </Terms>
-    </caa5aeb1a6644849b60fbe2335e12657>
-    <Year xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">2022</Year>
-    <a9b3b1dad23b4ba58c3f3e36a96e1d9c xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </a9b3b1dad23b4ba58c3f3e36a96e1d9c>
-    <j69a081f486747f6ac8a5aeed63facfd xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Public</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">a0c619ff-bd46-48f0-b213-6b7c03fe156d</TermId>
-        </TermInfo>
-      </Terms>
-    </j69a081f486747f6ac8a5aeed63facfd>
-    <_dlc_DocId xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">ESMA70-156-5314</_dlc_DocId>
-    <TaxCatchAll xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Value>8</Value>
-      <Value>5</Value>
-      <Value>424</Value>
-      <Value>24</Value>
-      <Value>421</Value>
-    </TaxCatchAll>
-    <MeetingDate xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e" xsi:nil="true"/>
-    <_dlc_DocIdUrl xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Url>https://securitiesandmarketsauth.sharepoint.com/sites/sherpa-trdu/_layouts/15/DocIdRedir.aspx?ID=ESMA70-156-5314</Url>
-      <Description>ESMA70-156-5314</Description>
-    </_dlc_DocIdUrl>
-    <bce29119141747ccb9ac7d87218ed4af xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Secondary Markets</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">0116aa60-aa30-4997-8f0f-29abf5f5f198</TermId>
-        </TermInfo>
-      </Terms>
-    </bce29119141747ccb9ac7d87218ed4af>
-    <n644e5dfaa29486bad4a4fc019c6d2df xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity - Amendment RTS 21</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">57d21c49-400b-4151-a958-bb4978c24367</TermId>
-        </TermInfo>
-      </Terms>
-    </n644e5dfaa29486bad4a4fc019c6d2df>
-    <eed0a0b2ea6941718a34434e243f3d8f xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Note</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">b9e1c92e-303a-4555-86f0-5c711c65937e</TermId>
-        </TermInfo>
-      </Terms>
-    </eed0a0b2ea6941718a34434e243f3d8f>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d8dec5-8a41-4471-b9ad-44c181776275">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="MiFID-MiFIR Policy Document" ma:contentTypeID="0x0101008D9E5D2C101BA04B85C7EB08C6516E40030200EF99A593C3F0614C8A5B6D644C171863" ma:contentTypeVersion="20" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="b8f6e82897e0191159aa619e7a133caf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e" xmlns:ns3="c3d8dec5-8a41-4471-b9ad-44c181776275" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a6fbef2c455e9b03649749803fe8f437" ns2:_="" ns3:_="">
     <xsd:import namespace="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e"/>
@@ -2553,77 +2545,115 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <caa5aeb1a6644849b60fbe2335e12657 xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">729cc5dc-fc40-4e6f-89b7-0bed773f437e</TermId>
+        </TermInfo>
+      </Terms>
+    </caa5aeb1a6644849b60fbe2335e12657>
+    <Year xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">2022</Year>
+    <a9b3b1dad23b4ba58c3f3e36a96e1d9c xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </a9b3b1dad23b4ba58c3f3e36a96e1d9c>
+    <j69a081f486747f6ac8a5aeed63facfd xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Public</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">a0c619ff-bd46-48f0-b213-6b7c03fe156d</TermId>
+        </TermInfo>
+      </Terms>
+    </j69a081f486747f6ac8a5aeed63facfd>
+    <_dlc_DocId xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">ESMA70-156-5314</_dlc_DocId>
+    <TaxCatchAll xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Value>8</Value>
+      <Value>5</Value>
+      <Value>424</Value>
+      <Value>24</Value>
+      <Value>421</Value>
+    </TaxCatchAll>
+    <MeetingDate xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e" xsi:nil="true"/>
+    <_dlc_DocIdUrl xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Url>https://securitiesandmarketsauth.sharepoint.com/sites/sherpa-trdu/_layouts/15/DocIdRedir.aspx?ID=ESMA70-156-5314</Url>
+      <Description>ESMA70-156-5314</Description>
+    </_dlc_DocIdUrl>
+    <bce29119141747ccb9ac7d87218ed4af xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Secondary Markets</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">0116aa60-aa30-4997-8f0f-29abf5f5f198</TermId>
+        </TermInfo>
+      </Terms>
+    </bce29119141747ccb9ac7d87218ed4af>
+    <n644e5dfaa29486bad4a4fc019c6d2df xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity - Amendment RTS 21</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">57d21c49-400b-4151-a958-bb4978c24367</TermId>
+        </TermInfo>
+      </Terms>
+    </n644e5dfaa29486bad4a4fc019c6d2df>
+    <eed0a0b2ea6941718a34434e243f3d8f xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Note</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">b9e1c92e-303a-4555-86f0-5c711c65937e</TermId>
+        </TermInfo>
+      </Terms>
+    </eed0a0b2ea6941718a34434e243f3d8f>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d8dec5-8a41-4471-b9ad-44c181776275">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8705E2CF-0D90-4DF6-9822-369FD84349CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E523DC75-AC58-42D4-91D6-ACB96E7D8BAC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38E6F263-81BF-4540-AA93-81177C473C94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4ABA636-273B-4741-B8A2-7A681221763B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4ABA636-273B-4741-B8A2-7A681221763B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38E6F263-81BF-4540-AA93-81177C473C94}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e"/>
+    <ds:schemaRef ds:uri="c3d8dec5-8a41-4471-b9ad-44c181776275"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E523DC75-AC58-42D4-91D6-ACB96E7D8BAC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8705E2CF-0D90-4DF6-9822-369FD84349CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e"/>
+    <ds:schemaRef ds:uri="c3d8dec5-8a41-4471-b9ad-44c181776275"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/positionlimit-previous.xlsx
+++ b/positionlimit-previous.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AC4897-5DDB-4E20-8C4C-758471988402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196A19DC-2437-4C50-8E21-24B1A2355B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="929" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31815" yWindow="2055" windowWidth="21600" windowHeight="12645" tabRatio="929" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Explanatory text" sheetId="1" r:id="rId1"/>
@@ -1799,7 +1799,7 @@
         <v>52</v>
       </c>
       <c r="N6" s="14">
-        <v>110000</v>
+        <v>50000</v>
       </c>
       <c r="O6" s="21">
         <v>21</v>
@@ -2201,65 +2201,73 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <caa5aeb1a6644849b60fbe2335e12657 xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">729cc5dc-fc40-4e6f-89b7-0bed773f437e</TermId>
+        </TermInfo>
+      </Terms>
+    </caa5aeb1a6644849b60fbe2335e12657>
+    <Year xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">2022</Year>
+    <a9b3b1dad23b4ba58c3f3e36a96e1d9c xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </a9b3b1dad23b4ba58c3f3e36a96e1d9c>
+    <j69a081f486747f6ac8a5aeed63facfd xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Public</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">a0c619ff-bd46-48f0-b213-6b7c03fe156d</TermId>
+        </TermInfo>
+      </Terms>
+    </j69a081f486747f6ac8a5aeed63facfd>
+    <_dlc_DocId xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">ESMA70-156-5314</_dlc_DocId>
+    <TaxCatchAll xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Value>8</Value>
+      <Value>5</Value>
+      <Value>424</Value>
+      <Value>24</Value>
+      <Value>421</Value>
+    </TaxCatchAll>
+    <MeetingDate xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e" xsi:nil="true"/>
+    <_dlc_DocIdUrl xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Url>https://securitiesandmarketsauth.sharepoint.com/sites/sherpa-trdu/_layouts/15/DocIdRedir.aspx?ID=ESMA70-156-5314</Url>
+      <Description>ESMA70-156-5314</Description>
+    </_dlc_DocIdUrl>
+    <bce29119141747ccb9ac7d87218ed4af xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Secondary Markets</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">0116aa60-aa30-4997-8f0f-29abf5f5f198</TermId>
+        </TermInfo>
+      </Terms>
+    </bce29119141747ccb9ac7d87218ed4af>
+    <n644e5dfaa29486bad4a4fc019c6d2df xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity - Amendment RTS 21</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">57d21c49-400b-4151-a958-bb4978c24367</TermId>
+        </TermInfo>
+      </Terms>
+    </n644e5dfaa29486bad4a4fc019c6d2df>
+    <eed0a0b2ea6941718a34434e243f3d8f xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Note</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">b9e1c92e-303a-4555-86f0-5c711c65937e</TermId>
+        </TermInfo>
+      </Terms>
+    </eed0a0b2ea6941718a34434e243f3d8f>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d8dec5-8a41-4471-b9ad-44c181776275">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="MiFID-MiFIR Policy Document" ma:contentTypeID="0x0101008D9E5D2C101BA04B85C7EB08C6516E40030200EF99A593C3F0614C8A5B6D644C171863" ma:contentTypeVersion="20" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="b8f6e82897e0191159aa619e7a133caf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e" xmlns:ns3="c3d8dec5-8a41-4471-b9ad-44c181776275" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a6fbef2c455e9b03649749803fe8f437" ns2:_="" ns3:_="">
     <xsd:import namespace="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e"/>
@@ -2545,90 +2553,77 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <caa5aeb1a6644849b60fbe2335e12657 xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">729cc5dc-fc40-4e6f-89b7-0bed773f437e</TermId>
-        </TermInfo>
-      </Terms>
-    </caa5aeb1a6644849b60fbe2335e12657>
-    <Year xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">2022</Year>
-    <a9b3b1dad23b4ba58c3f3e36a96e1d9c xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </a9b3b1dad23b4ba58c3f3e36a96e1d9c>
-    <j69a081f486747f6ac8a5aeed63facfd xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Public</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">a0c619ff-bd46-48f0-b213-6b7c03fe156d</TermId>
-        </TermInfo>
-      </Terms>
-    </j69a081f486747f6ac8a5aeed63facfd>
-    <_dlc_DocId xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">ESMA70-156-5314</_dlc_DocId>
-    <TaxCatchAll xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Value>8</Value>
-      <Value>5</Value>
-      <Value>424</Value>
-      <Value>24</Value>
-      <Value>421</Value>
-    </TaxCatchAll>
-    <MeetingDate xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e" xsi:nil="true"/>
-    <_dlc_DocIdUrl xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Url>https://securitiesandmarketsauth.sharepoint.com/sites/sherpa-trdu/_layouts/15/DocIdRedir.aspx?ID=ESMA70-156-5314</Url>
-      <Description>ESMA70-156-5314</Description>
-    </_dlc_DocIdUrl>
-    <bce29119141747ccb9ac7d87218ed4af xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Secondary Markets</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">0116aa60-aa30-4997-8f0f-29abf5f5f198</TermId>
-        </TermInfo>
-      </Terms>
-    </bce29119141747ccb9ac7d87218ed4af>
-    <n644e5dfaa29486bad4a4fc019c6d2df xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity - Amendment RTS 21</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">57d21c49-400b-4151-a958-bb4978c24367</TermId>
-        </TermInfo>
-      </Terms>
-    </n644e5dfaa29486bad4a4fc019c6d2df>
-    <eed0a0b2ea6941718a34434e243f3d8f xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Note</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">b9e1c92e-303a-4555-86f0-5c711c65937e</TermId>
-        </TermInfo>
-      </Terms>
-    </eed0a0b2ea6941718a34434e243f3d8f>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d8dec5-8a41-4471-b9ad-44c181776275">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E523DC75-AC58-42D4-91D6-ACB96E7D8BAC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8705E2CF-0D90-4DF6-9822-369FD84349CE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e"/>
+    <ds:schemaRef ds:uri="c3d8dec5-8a41-4471-b9ad-44c181776275"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4ABA636-273B-4741-B8A2-7A681221763B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38E6F263-81BF-4540-AA93-81177C473C94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2647,13 +2642,18 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4ABA636-273B-4741-B8A2-7A681221763B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8705E2CF-0D90-4DF6-9822-369FD84349CE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E523DC75-AC58-42D4-91D6-ACB96E7D8BAC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e"/>
-    <ds:schemaRef ds:uri="c3d8dec5-8a41-4471-b9ad-44c181776275"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/positionlimit-previous.xlsx
+++ b/positionlimit-previous.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29019"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196A19DC-2437-4C50-8E21-24B1A2355B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44ADC331-E6BC-4B44-A2A9-2A91F56553F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31815" yWindow="2055" windowWidth="21600" windowHeight="12645" tabRatio="929" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="929" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Explanatory text" sheetId="1" r:id="rId1"/>
@@ -382,7 +382,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -670,6 +670,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -685,6 +688,9 @@
     </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -734,41 +740,35 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="3" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1124,22 +1124,22 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A3:AH23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="13" max="13" width="4" customWidth="1"/>
     <col min="14" max="14" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="K3" s="32" t="s">
+    <row r="3" spans="1:34">
+      <c r="K3" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-    </row>
-    <row r="9" spans="1:34" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+    </row>
+    <row r="9" spans="1:34" s="6" customFormat="1" ht="34.5" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="3" t="s">
         <v>1</v>
@@ -1177,141 +1177,141 @@
       <c r="AG9" s="2"/>
       <c r="AH9" s="2"/>
     </row>
-    <row r="11" spans="1:34" s="8" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" s="8" customFormat="1" ht="17.45">
       <c r="B11" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:34" s="7" customFormat="1" ht="127.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="37" t="s">
+    <row r="12" spans="1:34" s="7" customFormat="1" ht="127.9" customHeight="1">
+      <c r="B12" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-    </row>
-    <row r="13" spans="1:34" s="7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-    </row>
-    <row r="14" spans="1:34" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+    </row>
+    <row r="13" spans="1:34" s="7" customFormat="1" ht="8.25" customHeight="1">
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+    </row>
+    <row r="14" spans="1:34" s="7" customFormat="1" ht="17.45">
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-    </row>
-    <row r="15" spans="1:34" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="37" t="s">
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" spans="1:34" s="7" customFormat="1" ht="75" customHeight="1">
+      <c r="B15" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
-      <c r="L15" s="37"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-    </row>
-    <row r="16" spans="1:34" s="7" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-    </row>
-    <row r="17" spans="2:14" s="7" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+    </row>
+    <row r="16" spans="1:34" s="7" customFormat="1" ht="10.5" customHeight="1">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+    </row>
+    <row r="17" spans="2:14" s="7" customFormat="1" ht="22.5" customHeight="1">
       <c r="B17" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-    </row>
-    <row r="18" spans="2:14" s="7" customFormat="1" ht="47.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="37" t="s">
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+    </row>
+    <row r="18" spans="2:14" s="7" customFormat="1" ht="47.65" customHeight="1">
+      <c r="B18" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-    </row>
-    <row r="19" spans="2:14" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-    </row>
-    <row r="20" spans="2:14" ht="18" x14ac:dyDescent="0.25">
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+    </row>
+    <row r="19" spans="2:14" ht="8.65" customHeight="1">
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="37"/>
+    </row>
+    <row r="20" spans="2:14" ht="17.45">
       <c r="B20" s="9" t="s">
         <v>8</v>
       </c>
@@ -1325,56 +1325,56 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="2:14" ht="49.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="37" t="s">
+    <row r="21" spans="2:14" ht="49.15" customHeight="1">
+      <c r="B21" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-    </row>
-    <row r="22" spans="2:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="37" t="s">
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+    </row>
+    <row r="22" spans="2:14" ht="36" customHeight="1">
+      <c r="B22" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-    </row>
-    <row r="23" spans="2:14" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="37" t="s">
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+    </row>
+    <row r="23" spans="2:14" ht="50.25" customHeight="1">
+      <c r="B23" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1399,7 +1399,7 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
@@ -1408,37 +1408,37 @@
     <col min="6" max="6" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-    </row>
-    <row r="2" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+    </row>
+    <row r="2" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>19</v>
       </c>
@@ -1458,43 +1458,43 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="33" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -1531,648 +1531,648 @@
     <col min="19" max="19" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:19" ht="18">
+      <c r="A1" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-    </row>
-    <row r="2" spans="1:19" s="13" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="42" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+    </row>
+    <row r="2" spans="1:19" s="14" customFormat="1" ht="13.9">
+      <c r="A2" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="45" t="s">
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45" t="s">
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-    </row>
-    <row r="3" spans="1:19" s="13" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="18"/>
+    </row>
+    <row r="3" spans="1:19" s="14" customFormat="1" ht="69">
+      <c r="A3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="R3" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="13" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:19" s="14" customFormat="1" ht="25.9" customHeight="1">
+      <c r="A4" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="15">
         <v>25050960</v>
       </c>
-      <c r="J4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4" s="16">
+      <c r="J4" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" s="17">
         <v>153017049</v>
       </c>
-      <c r="N4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q4" s="15" t="s">
+      <c r="N4" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q4" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="R4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="S4" s="27" t="s">
+      <c r="R4" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="S4" s="29" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="13" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:19" s="14" customFormat="1" ht="25.9" customHeight="1">
+      <c r="A5" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="15">
         <v>17938800</v>
       </c>
-      <c r="J5" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="M5" s="16">
+      <c r="J5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="17">
         <v>53054650</v>
       </c>
-      <c r="N5" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q5" s="15" t="s">
+      <c r="N5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="P5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="R5" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="S5" s="36" t="s">
+      <c r="R5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" s="46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:19" s="14" customFormat="1" ht="27.6">
+      <c r="A6" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="I6" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="J6" s="14">
+      <c r="I6" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="15">
         <v>20000</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="23">
         <v>12</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="15">
         <v>70000</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="N6" s="14">
-        <v>50000</v>
-      </c>
-      <c r="O6" s="21">
+      <c r="M6" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="N6" s="15">
+        <v>120000</v>
+      </c>
+      <c r="O6" s="23">
         <v>21</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="15">
         <v>100000</v>
       </c>
-      <c r="Q6" s="15" t="s">
+      <c r="Q6" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="R6" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="S6" s="25" t="s">
+      <c r="R6" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="S6" s="27" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:19" s="14" customFormat="1" ht="27.6">
+      <c r="A7" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="I7" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="J7" s="15">
+      <c r="I7" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="16">
         <v>2500</v>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="23">
         <v>12</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="16">
         <v>7500</v>
       </c>
-      <c r="M7" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="N7" s="14">
+      <c r="M7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="N7" s="15">
         <v>10000</v>
       </c>
-      <c r="O7" s="21">
+      <c r="O7" s="23">
         <v>21</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7" s="15">
         <v>7500</v>
       </c>
-      <c r="Q7" s="15" t="s">
+      <c r="Q7" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="R7" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="S7" s="26" t="s">
+      <c r="R7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="S7" s="28" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+    <row r="8" spans="1:19" s="14" customFormat="1" ht="27.6">
+      <c r="A8" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="14">
+      <c r="I8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="15">
         <v>7000</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="23">
         <v>12</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="15">
         <v>25000</v>
       </c>
-      <c r="M8" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="N8" s="14">
+      <c r="M8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="N8" s="15">
         <v>32000</v>
       </c>
-      <c r="O8" s="21">
+      <c r="O8" s="23">
         <v>21</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="15">
         <v>25000</v>
       </c>
-      <c r="Q8" s="15" t="s">
+      <c r="Q8" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="R8" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="S8" s="26" t="s">
+      <c r="R8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="S8" s="28" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="46" t="s">
+    <row r="9" spans="1:19" ht="7.9" customHeight="1"/>
+    <row r="10" spans="1:19" ht="7.5" customHeight="1"/>
+    <row r="11" spans="1:19" ht="18">
+      <c r="A11" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-    </row>
-    <row r="12" spans="1:19" s="13" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="42" t="s">
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45"/>
+      <c r="M11" s="45"/>
+      <c r="N11" s="45"/>
+      <c r="O11" s="45"/>
+      <c r="P11" s="45"/>
+      <c r="Q11" s="45"/>
+      <c r="R11" s="45"/>
+      <c r="S11" s="45"/>
+    </row>
+    <row r="12" spans="1:19" s="14" customFormat="1" ht="13.9">
+      <c r="A12" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="45" t="s">
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45" t="s">
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="N12" s="45"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
-    </row>
-    <row r="13" spans="1:19" s="13" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="18"/>
+    </row>
+    <row r="13" spans="1:19" s="14" customFormat="1" ht="69">
+      <c r="A13" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="N13" s="12" t="s">
+      <c r="N13" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="O13" s="12" t="s">
+      <c r="O13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="P13" s="12" t="s">
+      <c r="P13" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="Q13" s="12" t="s">
+      <c r="Q13" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="R13" s="12" t="s">
+      <c r="R13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="S13" s="12" t="s">
+      <c r="S13" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
+    <row r="14" spans="1:19" s="14" customFormat="1" ht="27.6">
+      <c r="A14" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="H14" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="31">
         <v>5951</v>
       </c>
-      <c r="J14" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="K14" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="L14" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="M14" s="23">
+      <c r="J14" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="25">
         <v>15837</v>
       </c>
-      <c r="N14" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="O14" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="P14" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q14" s="24" t="s">
+      <c r="N14" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="O14" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="P14" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q14" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="R14" s="24" t="s">
+      <c r="R14" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="S14" s="30" t="s">
+      <c r="S14" s="32" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="41" t="s">
+    <row r="16" spans="1:19" ht="27.4" customHeight="1">
+      <c r="A16" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="41"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40"/>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24"/>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="22"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
+      <c r="S18" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2201,70 +2201,53 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <caa5aeb1a6644849b60fbe2335e12657 xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">729cc5dc-fc40-4e6f-89b7-0bed773f437e</TermId>
-        </TermInfo>
-      </Terms>
-    </caa5aeb1a6644849b60fbe2335e12657>
-    <Year xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">2022</Year>
-    <a9b3b1dad23b4ba58c3f3e36a96e1d9c xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </a9b3b1dad23b4ba58c3f3e36a96e1d9c>
-    <j69a081f486747f6ac8a5aeed63facfd xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Public</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">a0c619ff-bd46-48f0-b213-6b7c03fe156d</TermId>
-        </TermInfo>
-      </Terms>
-    </j69a081f486747f6ac8a5aeed63facfd>
-    <_dlc_DocId xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">ESMA70-156-5314</_dlc_DocId>
-    <TaxCatchAll xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Value>8</Value>
-      <Value>5</Value>
-      <Value>424</Value>
-      <Value>24</Value>
-      <Value>421</Value>
-    </TaxCatchAll>
-    <MeetingDate xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e" xsi:nil="true"/>
-    <_dlc_DocIdUrl xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Url>https://securitiesandmarketsauth.sharepoint.com/sites/sherpa-trdu/_layouts/15/DocIdRedir.aspx?ID=ESMA70-156-5314</Url>
-      <Description>ESMA70-156-5314</Description>
-    </_dlc_DocIdUrl>
-    <bce29119141747ccb9ac7d87218ed4af xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Secondary Markets</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">0116aa60-aa30-4997-8f0f-29abf5f5f198</TermId>
-        </TermInfo>
-      </Terms>
-    </bce29119141747ccb9ac7d87218ed4af>
-    <n644e5dfaa29486bad4a4fc019c6d2df xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity - Amendment RTS 21</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">57d21c49-400b-4151-a958-bb4978c24367</TermId>
-        </TermInfo>
-      </Terms>
-    </n644e5dfaa29486bad4a4fc019c6d2df>
-    <eed0a0b2ea6941718a34434e243f3d8f xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Note</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">b9e1c92e-303a-4555-86f0-5c711c65937e</TermId>
-        </TermInfo>
-      </Terms>
-    </eed0a0b2ea6941718a34434e243f3d8f>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d8dec5-8a41-4471-b9ad-44c181776275">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2554,53 +2537,70 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <caa5aeb1a6644849b60fbe2335e12657 xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">729cc5dc-fc40-4e6f-89b7-0bed773f437e</TermId>
+        </TermInfo>
+      </Terms>
+    </caa5aeb1a6644849b60fbe2335e12657>
+    <Year xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">2022</Year>
+    <a9b3b1dad23b4ba58c3f3e36a96e1d9c xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </a9b3b1dad23b4ba58c3f3e36a96e1d9c>
+    <j69a081f486747f6ac8a5aeed63facfd xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Public</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">a0c619ff-bd46-48f0-b213-6b7c03fe156d</TermId>
+        </TermInfo>
+      </Terms>
+    </j69a081f486747f6ac8a5aeed63facfd>
+    <_dlc_DocId xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">ESMA70-156-5314</_dlc_DocId>
+    <TaxCatchAll xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Value>8</Value>
+      <Value>5</Value>
+      <Value>424</Value>
+      <Value>24</Value>
+      <Value>421</Value>
+    </TaxCatchAll>
+    <MeetingDate xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e" xsi:nil="true"/>
+    <_dlc_DocIdUrl xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Url>https://securitiesandmarketsauth.sharepoint.com/sites/sherpa-trdu/_layouts/15/DocIdRedir.aspx?ID=ESMA70-156-5314</Url>
+      <Description>ESMA70-156-5314</Description>
+    </_dlc_DocIdUrl>
+    <bce29119141747ccb9ac7d87218ed4af xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Secondary Markets</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">0116aa60-aa30-4997-8f0f-29abf5f5f198</TermId>
+        </TermInfo>
+      </Terms>
+    </bce29119141747ccb9ac7d87218ed4af>
+    <n644e5dfaa29486bad4a4fc019c6d2df xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity - Amendment RTS 21</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">57d21c49-400b-4151-a958-bb4978c24367</TermId>
+        </TermInfo>
+      </Terms>
+    </n644e5dfaa29486bad4a4fc019c6d2df>
+    <eed0a0b2ea6941718a34434e243f3d8f xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Note</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">b9e1c92e-303a-4555-86f0-5c711c65937e</TermId>
+        </TermInfo>
+      </Terms>
+    </eed0a0b2ea6941718a34434e243f3d8f>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d8dec5-8a41-4471-b9ad-44c181776275">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2613,47 +2613,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8705E2CF-0D90-4DF6-9822-369FD84349CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e"/>
-    <ds:schemaRef ds:uri="c3d8dec5-8a41-4471-b9ad-44c181776275"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4ABA636-273B-4741-B8A2-7A681221763B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38E6F263-81BF-4540-AA93-81177C473C94}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e"/>
-    <ds:schemaRef ds:uri="c3d8dec5-8a41-4471-b9ad-44c181776275"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38E6F263-81BF-4540-AA93-81177C473C94}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4ABA636-273B-4741-B8A2-7A681221763B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8705E2CF-0D90-4DF6-9822-369FD84349CE}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E523DC75-AC58-42D4-91D6-ACB96E7D8BAC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E523DC75-AC58-42D4-91D6-ACB96E7D8BAC}"/>
 </file>
--- a/positionlimit-previous.xlsx
+++ b/positionlimit-previous.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29019"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44ADC331-E6BC-4B44-A2A9-2A91F56553F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196A19DC-2437-4C50-8E21-24B1A2355B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="929" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31815" yWindow="2055" windowWidth="21600" windowHeight="12645" tabRatio="929" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Explanatory text" sheetId="1" r:id="rId1"/>
@@ -382,7 +382,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -670,9 +670,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -688,9 +685,6 @@
     </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -740,6 +734,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="3" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -766,9 +769,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="3" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1124,22 +1124,22 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A3:AH23"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="13" max="13" width="4" customWidth="1"/>
     <col min="14" max="14" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:34">
-      <c r="K3" s="34" t="s">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="K3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-    </row>
-    <row r="9" spans="1:34" s="6" customFormat="1" ht="34.5" customHeight="1">
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+    </row>
+    <row r="9" spans="1:34" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3" t="s">
         <v>1</v>
@@ -1177,141 +1177,141 @@
       <c r="AG9" s="2"/>
       <c r="AH9" s="2"/>
     </row>
-    <row r="11" spans="1:34" s="8" customFormat="1" ht="17.45">
+    <row r="11" spans="1:34" s="8" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:34" s="7" customFormat="1" ht="127.9" customHeight="1">
-      <c r="B12" s="36" t="s">
+    <row r="12" spans="1:34" s="7" customFormat="1" ht="127.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-    </row>
-    <row r="13" spans="1:34" s="7" customFormat="1" ht="8.25" customHeight="1">
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-    </row>
-    <row r="14" spans="1:34" s="7" customFormat="1" ht="17.45">
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+    </row>
+    <row r="13" spans="1:34" s="7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+    </row>
+    <row r="14" spans="1:34" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-    </row>
-    <row r="15" spans="1:34" s="7" customFormat="1" ht="75" customHeight="1">
-      <c r="B15" s="36" t="s">
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="34"/>
+    </row>
+    <row r="15" spans="1:34" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-    </row>
-    <row r="16" spans="1:34" s="7" customFormat="1" ht="10.5" customHeight="1">
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-    </row>
-    <row r="17" spans="2:14" s="7" customFormat="1" ht="22.5" customHeight="1">
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
+      <c r="N15" s="37"/>
+    </row>
+    <row r="16" spans="1:34" s="7" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+    </row>
+    <row r="17" spans="2:14" s="7" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-    </row>
-    <row r="18" spans="2:14" s="7" customFormat="1" ht="47.65" customHeight="1">
-      <c r="B18" s="36" t="s">
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+    </row>
+    <row r="18" spans="2:14" s="7" customFormat="1" ht="47.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-    </row>
-    <row r="19" spans="2:14" ht="8.65" customHeight="1">
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="37"/>
-    </row>
-    <row r="20" spans="2:14" ht="17.45">
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
+      <c r="N18" s="37"/>
+    </row>
+    <row r="19" spans="2:14" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+    </row>
+    <row r="20" spans="2:14" ht="18" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>8</v>
       </c>
@@ -1325,56 +1325,56 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="2:14" ht="49.15" customHeight="1">
-      <c r="B21" s="36" t="s">
+    <row r="21" spans="2:14" ht="49.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-    </row>
-    <row r="22" spans="2:14" ht="36" customHeight="1">
-      <c r="B22" s="36" t="s">
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="37"/>
+    </row>
+    <row r="22" spans="2:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-    </row>
-    <row r="23" spans="2:14" ht="50.25" customHeight="1">
-      <c r="B23" s="36" t="s">
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
+      <c r="N22" s="37"/>
+    </row>
+    <row r="23" spans="2:14" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1399,7 +1399,7 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
@@ -1408,37 +1408,37 @@
     <col min="6" max="6" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-    </row>
-    <row r="2" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+    </row>
+    <row r="2" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
+    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>19</v>
       </c>
@@ -1458,43 +1458,43 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="33" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="31" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="17" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -1531,648 +1531,648 @@
     <col min="19" max="19" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-    </row>
-    <row r="2" spans="1:19" s="14" customFormat="1" ht="13.9">
-      <c r="A2" s="41" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+    </row>
+    <row r="2" spans="1:19" s="13" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="44" t="s">
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44" t="s">
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-    </row>
-    <row r="3" spans="1:19" s="14" customFormat="1" ht="69">
-      <c r="A3" s="13" t="s">
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+    </row>
+    <row r="3" spans="1:19" s="13" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="Q3" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="13" t="s">
+      <c r="R3" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="13" t="s">
+      <c r="S3" s="12" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="14" customFormat="1" ht="25.9" customHeight="1">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:19" s="13" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="14">
         <v>25050960</v>
       </c>
-      <c r="J4" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="K4" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4" s="17">
+      <c r="J4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" s="16">
         <v>153017049</v>
       </c>
-      <c r="N4" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="O4" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="P4" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q4" s="16" t="s">
+      <c r="N4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="P4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q4" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="R4" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="S4" s="29" t="s">
+      <c r="R4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="S4" s="27" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="14" customFormat="1" ht="25.9" customHeight="1">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:19" s="13" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="14">
         <v>17938800</v>
       </c>
-      <c r="J5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="L5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="M5" s="17">
+      <c r="J5" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="16">
         <v>53054650</v>
       </c>
-      <c r="N5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q5" s="16" t="s">
+      <c r="N5" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="P5" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="R5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="S5" s="46" t="s">
+      <c r="R5" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" s="36" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="14" customFormat="1" ht="27.6">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:19" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="I6" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="J6" s="15">
+      <c r="I6" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="14">
         <v>20000</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="21">
         <v>12</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="14">
         <v>70000</v>
       </c>
-      <c r="M6" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="N6" s="15">
-        <v>120000</v>
-      </c>
-      <c r="O6" s="23">
+      <c r="M6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="N6" s="14">
+        <v>50000</v>
+      </c>
+      <c r="O6" s="21">
         <v>21</v>
       </c>
-      <c r="P6" s="15">
+      <c r="P6" s="14">
         <v>100000</v>
       </c>
-      <c r="Q6" s="16" t="s">
+      <c r="Q6" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="R6" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="S6" s="27" t="s">
+      <c r="R6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="S6" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="14" customFormat="1" ht="27.6">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:19" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="I7" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="J7" s="16">
+      <c r="I7" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="15">
         <v>2500</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="21">
         <v>12</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="15">
         <v>7500</v>
       </c>
-      <c r="M7" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="N7" s="15">
+      <c r="M7" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="N7" s="14">
         <v>10000</v>
       </c>
-      <c r="O7" s="23">
+      <c r="O7" s="21">
         <v>21</v>
       </c>
-      <c r="P7" s="15">
+      <c r="P7" s="14">
         <v>7500</v>
       </c>
-      <c r="Q7" s="16" t="s">
+      <c r="Q7" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="R7" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="S7" s="28" t="s">
+      <c r="R7" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="S7" s="26" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="14" customFormat="1" ht="27.6">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:19" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="15">
+      <c r="I8" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="14">
         <v>7000</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="21">
         <v>12</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="14">
         <v>25000</v>
       </c>
-      <c r="M8" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="N8" s="15">
+      <c r="M8" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="N8" s="14">
         <v>32000</v>
       </c>
-      <c r="O8" s="23">
+      <c r="O8" s="21">
         <v>21</v>
       </c>
-      <c r="P8" s="15">
+      <c r="P8" s="14">
         <v>25000</v>
       </c>
-      <c r="Q8" s="16" t="s">
+      <c r="Q8" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="R8" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="S8" s="28" t="s">
+      <c r="R8" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="S8" s="26" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.9" customHeight="1"/>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1"/>
-    <row r="11" spans="1:19" ht="18">
-      <c r="A11" s="45" t="s">
+    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="45"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="45"/>
-      <c r="S11" s="45"/>
-    </row>
-    <row r="12" spans="1:19" s="14" customFormat="1" ht="13.9">
-      <c r="A12" s="41" t="s">
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="46"/>
+    </row>
+    <row r="12" spans="1:19" s="13" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="44" t="s">
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="44" t="s">
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="18"/>
-    </row>
-    <row r="13" spans="1:19" s="14" customFormat="1" ht="69">
-      <c r="A13" s="13" t="s">
+      <c r="N12" s="45"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+    </row>
+    <row r="13" spans="1:19" s="13" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="13" t="s">
+      <c r="L13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="13" t="s">
+      <c r="M13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="N13" s="13" t="s">
+      <c r="N13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="O13" s="13" t="s">
+      <c r="O13" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="P13" s="13" t="s">
+      <c r="P13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="Q13" s="13" t="s">
+      <c r="Q13" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="R13" s="13" t="s">
+      <c r="R13" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="S13" s="13" t="s">
+      <c r="S13" s="12" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="14" customFormat="1" ht="27.6">
-      <c r="A14" s="30" t="s">
+    <row r="14" spans="1:19" s="13" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="30" t="s">
+      <c r="F14" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="29">
         <v>5951</v>
       </c>
-      <c r="J14" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="K14" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="L14" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="M14" s="25">
+      <c r="J14" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="23">
         <v>15837</v>
       </c>
-      <c r="N14" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="O14" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="P14" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q14" s="26" t="s">
+      <c r="N14" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="O14" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="P14" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q14" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="R14" s="26" t="s">
+      <c r="R14" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="S14" s="32" t="s">
+      <c r="S14" s="30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="27.4" customHeight="1">
-      <c r="A16" s="40" t="s">
+    <row r="16" spans="1:19" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="40"/>
-      <c r="S16" s="40"/>
-    </row>
-    <row r="17" spans="1:19">
-      <c r="A17" s="24" t="s">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="41"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-    </row>
-    <row r="18" spans="1:19">
-      <c r="A18" s="24" t="s">
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2201,53 +2201,70 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <caa5aeb1a6644849b60fbe2335e12657 xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">729cc5dc-fc40-4e6f-89b7-0bed773f437e</TermId>
+        </TermInfo>
+      </Terms>
+    </caa5aeb1a6644849b60fbe2335e12657>
+    <Year xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">2022</Year>
+    <a9b3b1dad23b4ba58c3f3e36a96e1d9c xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </a9b3b1dad23b4ba58c3f3e36a96e1d9c>
+    <j69a081f486747f6ac8a5aeed63facfd xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Public</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">a0c619ff-bd46-48f0-b213-6b7c03fe156d</TermId>
+        </TermInfo>
+      </Terms>
+    </j69a081f486747f6ac8a5aeed63facfd>
+    <_dlc_DocId xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">ESMA70-156-5314</_dlc_DocId>
+    <TaxCatchAll xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Value>8</Value>
+      <Value>5</Value>
+      <Value>424</Value>
+      <Value>24</Value>
+      <Value>421</Value>
+    </TaxCatchAll>
+    <MeetingDate xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e" xsi:nil="true"/>
+    <_dlc_DocIdUrl xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Url>https://securitiesandmarketsauth.sharepoint.com/sites/sherpa-trdu/_layouts/15/DocIdRedir.aspx?ID=ESMA70-156-5314</Url>
+      <Description>ESMA70-156-5314</Description>
+    </_dlc_DocIdUrl>
+    <bce29119141747ccb9ac7d87218ed4af xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Secondary Markets</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">0116aa60-aa30-4997-8f0f-29abf5f5f198</TermId>
+        </TermInfo>
+      </Terms>
+    </bce29119141747ccb9ac7d87218ed4af>
+    <n644e5dfaa29486bad4a4fc019c6d2df xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity - Amendment RTS 21</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">57d21c49-400b-4151-a958-bb4978c24367</TermId>
+        </TermInfo>
+      </Terms>
+    </n644e5dfaa29486bad4a4fc019c6d2df>
+    <eed0a0b2ea6941718a34434e243f3d8f xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Note</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">b9e1c92e-303a-4555-86f0-5c711c65937e</TermId>
+        </TermInfo>
+      </Terms>
+    </eed0a0b2ea6941718a34434e243f3d8f>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d8dec5-8a41-4471-b9ad-44c181776275">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2537,70 +2554,53 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <caa5aeb1a6644849b60fbe2335e12657 xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">729cc5dc-fc40-4e6f-89b7-0bed773f437e</TermId>
-        </TermInfo>
-      </Terms>
-    </caa5aeb1a6644849b60fbe2335e12657>
-    <Year xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">2022</Year>
-    <a9b3b1dad23b4ba58c3f3e36a96e1d9c xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </a9b3b1dad23b4ba58c3f3e36a96e1d9c>
-    <j69a081f486747f6ac8a5aeed63facfd xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Public</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">a0c619ff-bd46-48f0-b213-6b7c03fe156d</TermId>
-        </TermInfo>
-      </Terms>
-    </j69a081f486747f6ac8a5aeed63facfd>
-    <_dlc_DocId xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">ESMA70-156-5314</_dlc_DocId>
-    <TaxCatchAll xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Value>8</Value>
-      <Value>5</Value>
-      <Value>424</Value>
-      <Value>24</Value>
-      <Value>421</Value>
-    </TaxCatchAll>
-    <MeetingDate xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e" xsi:nil="true"/>
-    <_dlc_DocIdUrl xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Url>https://securitiesandmarketsauth.sharepoint.com/sites/sherpa-trdu/_layouts/15/DocIdRedir.aspx?ID=ESMA70-156-5314</Url>
-      <Description>ESMA70-156-5314</Description>
-    </_dlc_DocIdUrl>
-    <bce29119141747ccb9ac7d87218ed4af xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Secondary Markets</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">0116aa60-aa30-4997-8f0f-29abf5f5f198</TermId>
-        </TermInfo>
-      </Terms>
-    </bce29119141747ccb9ac7d87218ed4af>
-    <n644e5dfaa29486bad4a4fc019c6d2df xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Commodity - Amendment RTS 21</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">57d21c49-400b-4151-a958-bb4978c24367</TermId>
-        </TermInfo>
-      </Terms>
-    </n644e5dfaa29486bad4a4fc019c6d2df>
-    <eed0a0b2ea6941718a34434e243f3d8f xmlns="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Note</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">b9e1c92e-303a-4555-86f0-5c711c65937e</TermId>
-        </TermInfo>
-      </Terms>
-    </eed0a0b2ea6941718a34434e243f3d8f>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d8dec5-8a41-4471-b9ad-44c181776275">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2613,17 +2613,47 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4ABA636-273B-4741-B8A2-7A681221763B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8705E2CF-0D90-4DF6-9822-369FD84349CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e"/>
+    <ds:schemaRef ds:uri="c3d8dec5-8a41-4471-b9ad-44c181776275"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38E6F263-81BF-4540-AA93-81177C473C94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38E6F263-81BF-4540-AA93-81177C473C94}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d0fb0f98-34f9-4d57-9559-eb8efd17aa5e"/>
+    <ds:schemaRef ds:uri="c3d8dec5-8a41-4471-b9ad-44c181776275"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8705E2CF-0D90-4DF6-9822-369FD84349CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4ABA636-273B-4741-B8A2-7A681221763B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E523DC75-AC58-42D4-91D6-ACB96E7D8BAC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E523DC75-AC58-42D4-91D6-ACB96E7D8BAC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>